--- a/data/trans_orig/IP37-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP37-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8059</t>
+          <t>7530</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14140</t>
+          <t>13636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>14400</t>
+          <t>14561</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21748</t>
+          <t>21721</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>25050</t>
+          <t>24847</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33980</t>
+          <t>34017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>9050</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2189</t>
+          <t>2216</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>9376</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>39,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>6500</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15467</t>
+          <t>15670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26656</t>
+          <t>26350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>38918</t>
+          <t>38937</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>45,79%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17644</t>
+          <t>18000</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29764</t>
+          <t>29402</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>48518</t>
+          <t>49004</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>64677</t>
+          <t>65134</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,2%</t>
+          <t>44,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>59,33%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19297</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31559</t>
+          <t>31865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21799</t>
+          <t>22161</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>33919</t>
+          <t>33563</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>42,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>45101</t>
+          <t>44644</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>61260</t>
+          <t>60774</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>55,8%</t>
+          <t>55,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9428</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>18107</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18657</t>
+          <t>18661</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41474</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7532</t>
+          <t>7396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16075</t>
+          <t>16167</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4302</t>
+          <t>4317</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11234</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13925</t>
+          <t>13362</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24846</t>
+          <t>25308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,68%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17611</t>
+          <t>17505</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>24892</t>
+          <t>25032</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,41%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14455</t>
+          <t>15246</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>87,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34987</t>
+          <t>35581</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44903</t>
+          <t>45539</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>82,79%</t>
+          <t>83,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>3942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11363</t>
+          <t>11469</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3619</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10809</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>12,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>39,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>19251</t>
+          <t>18657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>16,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>35,49%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10192</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17593</t>
+          <t>17591</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12646</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18918</t>
+          <t>18929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>24755</t>
+          <t>24808</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35257</t>
+          <t>34933</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>82,19%</t>
+          <t>81,44%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4940</t>
+          <t>4942</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12426</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7717</t>
+          <t>7810</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>7639</t>
+          <t>7963</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18141</t>
+          <t>18088</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,17%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>9336</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>17229</t>
+          <t>17264</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,77%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,55%</t>
+          <t>71,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8238</t>
+          <t>8556</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>67,33%</t>
+          <t>67,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>19749</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30490</t>
+          <t>30260</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>63,55%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6816</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14817</t>
+          <t>14744</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,23%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>7691</t>
+          <t>7709</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15302</t>
+          <t>14984</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17129</t>
+          <t>17359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>27870</t>
+          <t>28335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>36,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>59,5%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>31580</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43537</t>
+          <t>43552</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>53,68%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>74,01%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>38749</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>52537</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74655</t>
+          <t>74497</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>92447</t>
+          <t>91734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,43%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>69,49%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15293</t>
+          <t>15278</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>27805</t>
+          <t>27250</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,99%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>20643</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>34769</t>
+          <t>34431</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>40276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>57355</t>
+          <t>57513</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,57%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>33544</t>
+          <t>33078</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>45987</t>
+          <t>45814</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>49,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>36727</t>
+          <t>36138</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49288</t>
+          <t>49261</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>73690</t>
+          <t>74976</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91741</t>
+          <t>92392</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>54,19%</t>
+          <t>55,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>67,47%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>20785</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33228</t>
+          <t>33694</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,76%</t>
+          <t>50,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>19940</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>32474</t>
+          <t>33063</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>46,93%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>44233</t>
+          <t>43582</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>60998</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>45,81%</t>
+          <t>44,86%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>170456</t>
+          <t>171440</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>197088</t>
+          <t>198509</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>56,54%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>65,37%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>187220</t>
+          <t>188033</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>214065</t>
+          <t>215929</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,33%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>365387</t>
+          <t>366403</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>404206</t>
+          <t>403945</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>59,08%</t>
+          <t>59,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,32%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>104400</t>
+          <t>102979</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>131032</t>
+          <t>130048</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,63%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>43,46%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>102878</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>129723</t>
+          <t>128910</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,67%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>214225</t>
+          <t>214486</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>253044</t>
+          <t>252028</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,68%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,75%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>23765</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31415</t>
+          <t>31371</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24511</t>
+          <t>25516</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>32163</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,44%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52628</t>
+          <t>52188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>62352</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,62%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1552</t>
+          <t>1596</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9183</t>
+          <t>9202</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1807</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9325</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,56%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14615</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>28148</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39814</t>
+          <t>40012</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>51,27%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37331</t>
+          <t>38419</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>51437</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>51,39%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>69,91%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>70307</t>
+          <t>69774</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89022</t>
+          <t>87711</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>14763</t>
+          <t>14565</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>26429</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>48,73%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21857</t>
+          <t>21211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>35317</t>
+          <t>34229</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,61%</t>
+          <t>47,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>38204</t>
+          <t>39515</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>57452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,16%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26425</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36136</t>
+          <t>36309</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,19%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>82,31%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25549</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35046</t>
+          <t>35313</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>56,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>55309</t>
+          <t>54424</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69526</t>
+          <t>69051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>78,84%</t>
+          <t>78,3%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7765</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,81%</t>
+          <t>40,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9239</t>
+          <t>8972</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>18660</t>
+          <t>19135</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>32877</t>
+          <t>33762</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,28%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30329</t>
+          <t>30512</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38216</t>
+          <t>37992</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>91,91%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>31099</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39649</t>
+          <t>39543</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,84%</t>
+          <t>93,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>64557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76433</t>
+          <t>75867</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,5%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11252</t>
+          <t>11069</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2604</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>11154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7401</t>
+          <t>7967</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18769</t>
+          <t>19277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19189</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>26356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13899</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22484</t>
+          <t>22415</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36308</t>
+          <t>35411</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>47362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,25%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2135</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9522</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>32,71%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5018</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13030</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>8887</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20802</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>37,01%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20304</t>
+          <t>21270</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29657</t>
+          <t>29697</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>17355</t>
+          <t>16913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26673</t>
+          <t>26729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>54714</t>
+          <t>54195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,14%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5303</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14656</t>
+          <t>13690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10496</t>
+          <t>10440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>19814</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>54,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57147</t>
+          <t>56870</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68436</t>
+          <t>68298</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>52828</t>
+          <t>52763</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>65834</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>65,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>114373</t>
+          <t>114837</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>131781</t>
+          <t>131764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,75%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8795</t>
+          <t>8933</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>20084</t>
+          <t>20361</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>14273</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>27279</t>
+          <t>27344</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>25557</t>
+          <t>25574</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>42965</t>
+          <t>42501</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>50947</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>62410</t>
+          <t>62439</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54798</t>
+          <t>55251</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66187</t>
+          <t>66269</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108977</t>
+          <t>109227</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125874</t>
+          <t>126402</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>83,13%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>12759</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>24349</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10706</t>
+          <t>10624</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22095</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>26187</t>
+          <t>25659</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43084</t>
+          <t>42834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,17%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>284784</t>
+          <t>284619</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>312239</t>
+          <t>312540</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>73,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>290227</t>
+          <t>287798</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>317646</t>
+          <t>318138</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>580782</t>
+          <t>582699</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>623064</t>
+          <t>623538</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>77,57%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>76858</t>
+          <t>76557</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>104313</t>
+          <t>104478</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>97047</t>
+          <t>96555</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124466</t>
+          <t>126895</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>180726</t>
+          <t>180252</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>223008</t>
+          <t>221091</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>23690</t>
+          <t>23740</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29475</t>
+          <t>29535</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17541</t>
+          <t>16698</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26335</t>
+          <t>25650</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>51,99%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>79,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>43206</t>
+          <t>43741</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54410</t>
+          <t>54348</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>69,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,21%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1453</t>
+          <t>1393</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7238</t>
+          <t>7188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5780</t>
+          <t>6465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8633</t>
+          <t>8695</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19837</t>
+          <t>19302</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36384</t>
+          <t>35155</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49055</t>
+          <t>48754</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41297</t>
+          <t>41138</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>54483</t>
+          <t>53976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>56,13%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80553</t>
+          <t>80007</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>99568</t>
+          <t>98675</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>71,03%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17547</t>
+          <t>17848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30218</t>
+          <t>31447</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>45,37%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>19093</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32279</t>
+          <t>32438</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>40609</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>59624</t>
+          <t>60170</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,92%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>25715</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33092</t>
+          <t>33087</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>72,18%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>21600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28409</t>
+          <t>28403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>92,96%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>49713</t>
+          <t>49674</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59966</t>
+          <t>59721</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>90,54%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2307</t>
+          <t>2312</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9684</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,82%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2150</t>
+          <t>2156</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9363</t>
+          <t>8959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5992</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16245</t>
+          <t>16284</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,69%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31449</t>
+          <t>32148</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40682</t>
+          <t>40631</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36392</t>
+          <t>36024</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>45136</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,84%</t>
+          <t>75,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71554</t>
+          <t>72810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84002</t>
+          <t>84320</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3028</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12210</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>11962</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,16%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>7325</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>20091</t>
+          <t>18835</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19554</t>
+          <t>19586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>26398</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,38%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19987</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>24175</t>
+          <t>24190</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>79,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42357</t>
+          <t>41929</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>49997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,23%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8715</t>
+          <t>8683</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>600</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4803</t>
+          <t>5180</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2929</t>
+          <t>3061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10701</t>
+          <t>11129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10627</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19034</t>
+          <t>19039</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4902</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13315</t>
+          <t>13407</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>29841</t>
+          <t>29530</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,46%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17329</t>
+          <t>17307</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11980</t>
+          <t>11888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20393</t>
+          <t>20575</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>23410</t>
+          <t>23721</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35889</t>
+          <t>35391</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,96%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>66,46%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25621</t>
+          <t>25346</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36148</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>73,44%</t>
+          <t>72,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>32263</t>
+          <t>31992</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43368</t>
+          <t>43905</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61116</t>
+          <t>61328</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76339</t>
+          <t>77161</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>72,84%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13183</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>24018</t>
+          <t>24293</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>27,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11797</t>
+          <t>11260</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>22902</t>
+          <t>23173</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,51%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>28465</t>
+          <t>27643</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>43688</t>
+          <t>43476</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>41,68%</t>
+          <t>41,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>64475</t>
+          <t>64248</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>73553</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>54897</t>
+          <t>54911</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>66554</t>
+          <t>66725</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123070</t>
+          <t>122314</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138687</t>
+          <t>138188</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>87,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>5658</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15403</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>22460</t>
+          <t>22446</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>18548</t>
+          <t>19047</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>34165</t>
+          <t>34921</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>22,21%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>262856</t>
+          <t>263178</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288726</t>
+          <t>289108</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,69%</t>
+          <t>79,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>255559</t>
+          <t>254604</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>283291</t>
+          <t>282717</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>525049</t>
+          <t>526669</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>563719</t>
+          <t>564503</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,42%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>73603</t>
+          <t>73221</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>99473</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83551</t>
+          <t>84125</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>111283</t>
+          <t>112238</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>165452</t>
+          <t>164668</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>204122</t>
+          <t>202502</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,77%</t>
         </is>
       </c>
     </row>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>15976</t>
+          <t>16025</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26363</t>
+          <t>26329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12967</t>
+          <t>12833</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20540</t>
+          <t>20301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33575</t>
+          <t>33319</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>45195</t>
+          <t>45856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>65,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>90,4%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1365</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>11669</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2491</t>
+          <t>2730</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10064</t>
+          <t>10198</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>44,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5531</t>
+          <t>4870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17407</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>44344</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>66109</t>
+          <t>65624</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33951</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47811</t>
+          <t>48495</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85907</t>
+          <t>85701</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114080</t>
+          <t>113919</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,13%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3833</t>
+          <t>4318</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>25598</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11504</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>25364</t>
+          <t>24273</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>42,76%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15177</t>
+          <t>15338</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>43350</t>
+          <t>43556</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>33,54%</t>
+          <t>33,7%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11963</t>
+          <t>12135</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18034</t>
+          <t>18020</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>13797</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22734</t>
+          <t>22201</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>29279</t>
+          <t>29353</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>39690</t>
+          <t>39120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>81,83%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2280</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8351</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4758</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13695</t>
+          <t>13093</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>47,63%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8686</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>38,75%</t>
+          <t>38,6%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9600</t>
+          <t>9716</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18901</t>
+          <t>19345</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6909</t>
+          <t>6839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15353</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31930</t>
+          <t>32563</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>47,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>75,57%</t>
+          <t>77,07%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5324</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15069</t>
+          <t>14953</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2232</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10676</t>
+          <t>10746</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23078</t>
+          <t>22138</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,43%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>531</t>
+          <t>425</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1445</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5324</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2694</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>7297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>26,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>68,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3077</t>
+          <t>3183</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1757</t>
+          <t>1724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5636</t>
+          <t>5544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3444</t>
+          <t>3392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7995</t>
+          <t>7889</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>73,8%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19660</t>
+          <t>19684</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>54,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>12081</t>
+          <t>11980</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18319</t>
+          <t>18552</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>28073</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>36837</t>
+          <t>36910</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>62,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,73%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10227</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>45,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2666</t>
+          <t>2433</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8904</t>
+          <t>9005</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7776</t>
+          <t>7703</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>16336</t>
+          <t>16540</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23751</t>
+          <t>24266</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>33384</t>
+          <t>33417</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34744</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>44585</t>
+          <t>44809</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>61637</t>
+          <t>62582</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>75601</t>
+          <t>76342</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>88,55%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5158</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14791</t>
+          <t>14276</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3081</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>12474</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10608</t>
+          <t>9867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>24572</t>
+          <t>23627</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17882</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29454</t>
+          <t>29557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>23123</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>36215</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>68,04%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>44210</t>
+          <t>44981</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62228</t>
+          <t>63194</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>60,7%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>19792</t>
+          <t>19689</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>31364</t>
+          <t>31801</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>17023</t>
+          <t>17054</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>30136</t>
+          <t>30146</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>39321</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58305</t>
+          <t>57534</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>162495</t>
+          <t>163670</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204839</t>
+          <t>205255</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>162932</t>
+          <t>164795</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>192773</t>
+          <t>193078</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>338564</t>
+          <t>339051</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>390416</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>95149</t>
+          <t>93974</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>63651</t>
+          <t>63346</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>93492</t>
+          <t>91629</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>123652</t>
+          <t>125858</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>175504</t>
+          <t>175017</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,14%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
